--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561463642</v>
+        <v>46157.93067272612</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93067272612</v>
+        <v>46157.93151838842</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93151838842</v>
+        <v>46157.93393172995</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393172995</v>
+        <v>46157.93707383609</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93707383609</v>
+        <v>46158.28210214306</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210214306</v>
+        <v>46158.2966509429</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2966509429</v>
+        <v>46158.29804096255</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804096255</v>
+        <v>46158.3338091102</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3338091102</v>
+        <v>46158.36847204893</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Август/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847204893</v>
+        <v>46158.37281150618</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
